--- a/Filtered/HCA_Florida_Raulerson_Hospital.xlsx
+++ b/Filtered/HCA_Florida_Raulerson_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1306,6 +1361,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1862,6 +1957,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1919,6 +2019,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2708,6 +2868,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2862,6 +3032,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2996,6 +3176,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3053,6 +3238,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3130,6 +3320,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3187,6 +3382,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3249,6 +3449,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3383,6 +3593,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3517,6 +3737,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3651,6 +3881,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3785,6 +4025,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3976,6 +4231,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4130,6 +4395,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4264,6 +4539,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4398,6 +4683,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +4827,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4589,6 +4889,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4666,6 +4971,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4723,6 +5033,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4800,6 +5115,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4857,6 +5177,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4934,6 +5259,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4991,6 +5321,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5068,6 +5403,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5145,6 +5485,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5202,6 +5547,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5279,6 +5629,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5336,6 +5691,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5398,6 +5758,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5455,6 +5820,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5532,6 +5902,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5589,6 +5964,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5666,6 +6046,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5723,6 +6108,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5800,6 +6190,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5857,6 +6252,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5934,6 +6334,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5991,6 +6396,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6068,6 +6478,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6125,6 +6540,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6202,6 +6622,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6259,6 +6684,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6336,6 +6766,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6393,6 +6828,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6470,6 +6910,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6527,6 +6972,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6604,6 +7054,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6661,6 +7116,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6738,6 +7198,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6795,6 +7260,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6872,6 +7342,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6929,6 +7404,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7006,6 +7486,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7063,6 +7548,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7140,6 +7630,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7197,6 +7692,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7274,6 +7774,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7331,6 +7836,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7408,6 +7918,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7465,6 +7980,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7542,6 +8062,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7599,6 +8124,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7676,6 +8206,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7733,6 +8268,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7810,6 +8350,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7867,6 +8412,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7944,6 +8494,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8021,6 +8576,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8078,6 +8638,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8155,6 +8720,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8232,6 +8802,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8289,6 +8864,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8366,6 +8946,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8423,6 +9008,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8500,6 +9090,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8577,6 +9172,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8634,6 +9234,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8711,6 +9316,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8768,6 +9378,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8845,6 +9460,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8922,6 +9542,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8979,6 +9604,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9056,6 +9686,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9113,6 +9748,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9190,6 +9830,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9247,6 +9892,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9309,6 +9959,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9366,6 +10021,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9443,6 +10103,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9500,6 +10165,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9562,6 +10232,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9619,6 +10294,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9681,6 +10361,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9738,6 +10423,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9815,6 +10505,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9872,6 +10567,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9949,6 +10649,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10006,6 +10711,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10083,6 +10793,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10140,6 +10855,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10217,6 +10937,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10274,6 +10999,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10351,6 +11081,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10408,6 +11143,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10485,6 +11225,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10542,6 +11287,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10619,6 +11369,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10676,6 +11431,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10753,6 +11513,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10810,6 +11575,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10887,6 +11657,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10944,6 +11719,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11021,6 +11801,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11078,6 +11863,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11155,6 +11945,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11212,6 +12007,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11289,6 +12089,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11346,6 +12151,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11423,6 +12233,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11480,6 +12295,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11557,6 +12377,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11634,6 +12459,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11691,6 +12521,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11753,6 +12588,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11810,6 +12650,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11872,6 +12717,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11929,6 +12779,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12006,6 +12861,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12063,6 +12923,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12140,6 +13005,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12197,6 +13067,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12274,6 +13149,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12331,6 +13211,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12408,6 +13293,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12465,6 +13355,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12542,6 +13437,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12599,6 +13499,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12676,6 +13581,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12733,6 +13643,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12810,6 +13725,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12867,6 +13787,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12944,6 +13869,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13001,6 +13931,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13078,6 +14013,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13135,6 +14075,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13212,6 +14157,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13269,6 +14219,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13346,6 +14301,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13403,6 +14363,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13480,6 +14445,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13537,6 +14507,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13614,6 +14589,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13671,6 +14651,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13748,6 +14733,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13805,6 +14795,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13882,6 +14877,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13939,6 +14939,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14016,6 +15021,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14073,6 +15083,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14150,6 +15165,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14207,6 +15227,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14284,6 +15309,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14341,6 +15371,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14418,6 +15453,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14475,6 +15515,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14552,6 +15597,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14609,6 +15659,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14686,6 +15741,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14743,6 +15803,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14820,6 +15885,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14877,6 +15947,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14954,6 +16029,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15011,6 +16091,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15088,6 +16173,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15145,6 +16235,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15222,6 +16317,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15279,6 +16379,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15356,6 +16461,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15413,6 +16523,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15490,6 +16605,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15547,6 +16667,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15609,6 +16734,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15666,6 +16796,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15743,6 +16878,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15800,6 +16940,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15877,6 +17022,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15934,6 +17084,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16011,6 +17166,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16088,6 +17248,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16145,6 +17310,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16222,6 +17392,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16279,6 +17454,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16356,6 +17536,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16413,6 +17598,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16490,6 +17680,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16547,6 +17742,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16624,6 +17824,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16681,6 +17886,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16758,6 +17968,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16815,6 +18030,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16892,6 +18112,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16949,6 +18174,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17026,6 +18256,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17083,6 +18318,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17160,6 +18400,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17217,6 +18462,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17294,6 +18544,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17351,6 +18606,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17428,6 +18688,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17485,6 +18750,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17547,6 +18817,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17604,6 +18879,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17681,6 +18961,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17738,6 +19023,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17815,6 +19105,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17872,6 +19167,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17949,6 +19249,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18006,6 +19311,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18083,6 +19393,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18140,6 +19455,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18217,6 +19537,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18274,6 +19599,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18351,6 +19681,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18408,6 +19743,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18485,6 +19825,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18542,6 +19887,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18619,6 +19969,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18676,6 +20031,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18753,6 +20113,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18810,6 +20175,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18887,6 +20257,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18944,6 +20319,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19021,6 +20401,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19078,6 +20463,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19155,6 +20545,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19212,6 +20607,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19289,6 +20689,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19346,6 +20751,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19423,6 +20833,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19500,6 +20915,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19557,6 +20977,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19634,6 +21059,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19691,6 +21121,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19768,6 +21203,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19825,6 +21265,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19902,6 +21347,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19979,6 +21429,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20036,6 +21491,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20113,6 +21573,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20170,6 +21635,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20247,6 +21717,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20324,6 +21799,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20381,6 +21861,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20458,6 +21943,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20515,6 +22005,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20592,6 +22087,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20649,6 +22149,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20711,6 +22216,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20768,6 +22278,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20845,6 +22360,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20902,6 +22422,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20979,6 +22504,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21036,6 +22566,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21113,6 +22648,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21170,6 +22710,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21232,6 +22777,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21289,6 +22839,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21366,6 +22921,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21423,6 +22983,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21500,6 +23065,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21557,6 +23127,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21634,6 +23209,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21691,6 +23271,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21768,6 +23353,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21825,6 +23415,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21902,6 +23497,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21959,6 +23559,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22036,6 +23641,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22093,6 +23703,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22170,6 +23785,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22227,6 +23847,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22289,6 +23914,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22346,6 +23976,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22423,6 +24058,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22480,6 +24120,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22557,6 +24202,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22614,6 +24264,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22691,6 +24346,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22748,6 +24408,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22825,6 +24490,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22882,6 +24552,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22959,6 +24634,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23016,6 +24696,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23093,6 +24778,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23150,6 +24840,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23227,6 +24922,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23284,6 +24984,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23361,6 +25066,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23418,6 +25128,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23495,6 +25210,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23552,6 +25272,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23629,6 +25354,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23686,6 +25416,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23763,6 +25498,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23820,6 +25560,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23897,6 +25642,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23954,6 +25704,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24031,6 +25786,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24088,6 +25848,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24165,6 +25930,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24222,6 +25992,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24284,6 +26059,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24346,6 +26126,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24408,6 +26193,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24465,6 +26255,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24542,6 +26337,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24599,6 +26399,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24661,6 +26466,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24723,6 +26533,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24785,6 +26600,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24847,6 +26667,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24909,6 +26734,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24966,6 +26796,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25043,6 +26878,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25100,6 +26940,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25177,6 +27022,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25234,6 +27084,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25296,6 +27151,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25358,6 +27218,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25415,6 +27280,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25492,6 +27362,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25549,6 +27424,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25626,6 +27506,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25683,6 +27568,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25745,6 +27635,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25807,6 +27702,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25869,6 +27769,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25926,6 +27831,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26003,6 +27913,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26060,6 +27975,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26137,6 +28057,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26194,6 +28119,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26256,6 +28186,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26313,6 +28248,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26375,6 +28315,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26437,6 +28382,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26494,6 +28444,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26556,6 +28511,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26618,6 +28578,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26680,6 +28645,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26737,6 +28707,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26814,6 +28789,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26871,6 +28851,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26933,6 +28918,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26995,6 +28985,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27057,6 +29052,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27114,6 +29114,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27176,6 +29181,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27238,6 +29248,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27300,6 +29315,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27357,6 +29377,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27434,6 +29459,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27491,6 +29521,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27553,6 +29588,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27610,6 +29650,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27687,6 +29732,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27744,6 +29794,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27806,6 +29861,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27868,6 +29928,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27930,6 +29995,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27987,6 +30057,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28064,6 +30139,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28121,6 +30201,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28198,6 +30283,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28255,6 +30345,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28317,6 +30412,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28379,6 +30479,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28436,6 +30541,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28498,6 +30608,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28560,6 +30675,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28622,6 +30742,11 @@
           <t>COCQR</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28677,6 +30802,11 @@
       <c r="K427" t="inlineStr">
         <is>
           <t>COCQR</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
